--- a/artfynd/A 43978-2025 artfynd.xlsx
+++ b/artfynd/A 43978-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114569815</v>
+        <v>114569811</v>
       </c>
       <c r="B2" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>817412</v>
+        <v>817392</v>
       </c>
       <c r="R2" t="n">
-        <v>7305252</v>
+        <v>7305272</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114569817</v>
+        <v>114569813</v>
       </c>
       <c r="B3" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>817409</v>
+        <v>817406</v>
       </c>
       <c r="R3" t="n">
-        <v>7305262</v>
+        <v>7305255</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114569811</v>
+        <v>114569815</v>
       </c>
       <c r="B4" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>817392</v>
+        <v>817412</v>
       </c>
       <c r="R4" t="n">
-        <v>7305272</v>
+        <v>7305252</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114569823</v>
+        <v>114569817</v>
       </c>
       <c r="B5" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>817415</v>
+        <v>817409</v>
       </c>
       <c r="R5" t="n">
-        <v>7305284</v>
+        <v>7305262</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114569825</v>
+        <v>114569819</v>
       </c>
       <c r="B6" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>817420</v>
+        <v>817408</v>
       </c>
       <c r="R6" t="n">
-        <v>7305298</v>
+        <v>7305272</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,12 +1183,7 @@
         <v>114569821</v>
       </c>
       <c r="B7" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114570015</v>
+        <v>114569823</v>
       </c>
       <c r="B8" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>817408</v>
+        <v>817415</v>
       </c>
       <c r="R8" t="n">
-        <v>7305272</v>
+        <v>7305284</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114569813</v>
+        <v>114569825</v>
       </c>
       <c r="B9" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>817406</v>
+        <v>817420</v>
       </c>
       <c r="R9" t="n">
-        <v>7305255</v>
+        <v>7305298</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,6 +1480,107 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>114570011</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Norrbotten, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>817438</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7305305</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nederluleå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Björn Almqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43978-2025 artfynd.xlsx
+++ b/artfynd/A 43978-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114569811</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114569813</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114569815</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114569817</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114569819</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114569821</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114569823</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114569825</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,8 +1626,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114570011</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>